--- a/data/final/tables/repr_bootstrap.xlsx
+++ b/data/final/tables/repr_bootstrap.xlsx
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6668282999999999</v>
+        <v>0.6670725000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0.667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.638</v>
+        <v>0.637</v>
       </c>
       <c r="F3" t="n">
         <v>0.696</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01488551567691548</v>
+        <v>0.01488151167351519</v>
       </c>
       <c r="H3" t="n">
         <v>10000</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6163351999999999</v>
+        <v>0.6160258000000001</v>
       </c>
       <c r="D4" t="n">
         <v>0.616</v>
@@ -554,7 +554,7 @@
         <v>0.646</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01532590386544721</v>
+        <v>0.01536847270731012</v>
       </c>
       <c r="H4" t="n">
         <v>10000</v>
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04111326562707372</v>
+        <v>0.0413465642335767</v>
       </c>
       <c r="D5" t="n">
         <v>0.0412534837425349</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01225348374253488</v>
+        <v>0.01125348374253488</v>
       </c>
       <c r="F5" t="n">
         <v>0.07025348374253482</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01479833311972654</v>
+        <v>0.01482422941993154</v>
       </c>
       <c r="H5" t="n">
         <v>10000</v>
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01442323092236231</v>
+        <v>0.01466052727272727</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01225348374253488</v>
+        <v>0.01274651625746515</v>
       </c>
       <c r="E6" t="n">
         <v>0.0007465162574651352</v>
@@ -614,7 +614,7 @@
         <v>0.03974651625746517</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01074312179419131</v>
+        <v>0.01075821420687744</v>
       </c>
       <c r="H6" t="n">
         <v>10000</v>
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.06570274793213159</v>
+        <v>0.06607558038176042</v>
       </c>
       <c r="D7" t="n">
         <v>0.06592682926829278</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01958218451749741</v>
+        <v>0.01798409331919412</v>
       </c>
       <c r="F7" t="n">
         <v>0.112271474019088</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02364908590819502</v>
+        <v>0.02369047055762124</v>
       </c>
       <c r="H7" t="n">
         <v>10000</v>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02304963838812301</v>
+        <v>0.02342885959703075</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01958218451749741</v>
+        <v>0.02037009544008481</v>
       </c>
       <c r="E8" t="n">
         <v>0.001193001060445343</v>
@@ -674,7 +674,7 @@
         <v>0.06351855779427361</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01716848838159735</v>
+        <v>0.01719260743347221</v>
       </c>
       <c r="H8" t="n">
         <v>10000</v>
@@ -692,19 +692,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.570274793213158</v>
+        <v>6.607558038176043</v>
       </c>
       <c r="D9" t="n">
         <v>6.592682926829278</v>
       </c>
       <c r="E9" t="n">
-        <v>1.958218451749741</v>
+        <v>1.798409331919412</v>
       </c>
       <c r="F9" t="n">
         <v>11.2271474019088</v>
       </c>
       <c r="G9" t="n">
-        <v>2.364908590819502</v>
+        <v>2.369047055762124</v>
       </c>
       <c r="H9" t="n">
         <v>10000</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.304963838812301</v>
+        <v>2.342885959703076</v>
       </c>
       <c r="D10" t="n">
-        <v>1.958218451749741</v>
+        <v>2.037009544008481</v>
       </c>
       <c r="E10" t="n">
         <v>0.1193001060445343</v>
@@ -734,7 +734,7 @@
         <v>6.35185577942736</v>
       </c>
       <c r="G10" t="n">
-        <v>1.716848838159735</v>
+        <v>1.719260743347221</v>
       </c>
       <c r="H10" t="n">
         <v>10000</v>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9342972520678684</v>
+        <v>0.9339244196182395</v>
       </c>
       <c r="D11" t="n">
         <v>0.9340731707317073</v>
@@ -761,10 +761,10 @@
         <v>0.887728525980912</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9804178154825026</v>
+        <v>0.9820159066808059</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02364908590819502</v>
+        <v>0.02369047055762124</v>
       </c>
       <c r="H11" t="n">
         <v>10000</v>
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9769503616118769</v>
+        <v>0.9765711404029693</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9804178154825026</v>
+        <v>0.9796299045599152</v>
       </c>
       <c r="E12" t="n">
         <v>0.9364814422057264</v>
@@ -794,7 +794,7 @@
         <v>0.9988069989395546</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01716848838159734</v>
+        <v>0.01719260743347221</v>
       </c>
       <c r="H12" t="n">
         <v>10000</v>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.2080608</v>
+        <v>38.2019619</v>
       </c>
       <c r="D14" t="n">
-        <v>38.20950000000001</v>
+        <v>38.2</v>
       </c>
       <c r="E14" t="n">
-        <v>37.585</v>
+        <v>37.584</v>
       </c>
       <c r="F14" t="n">
-        <v>38.834</v>
+        <v>38.829</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3169435773548387</v>
+        <v>0.319358947678214</v>
       </c>
       <c r="H14" t="n">
         <v>10000</v>
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39.19902975165142</v>
+        <v>39.19819342238151</v>
       </c>
       <c r="D15" t="n">
-        <v>39.1992989983972</v>
+        <v>39.193</v>
       </c>
       <c r="E15" t="n">
-        <v>38.54108011022044</v>
+        <v>38.56156156156156</v>
       </c>
       <c r="F15" t="n">
-        <v>39.86288447766403</v>
+        <v>39.868</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3373482355480265</v>
+        <v>0.332288617281822</v>
       </c>
       <c r="H15" t="n">
         <v>10000</v>
@@ -902,19 +902,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6636189218718896</v>
+        <v>0.6699952089943589</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6577419515433114</v>
+        <v>0.6672419515433106</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08074514603385279</v>
+        <v>0.08524195154331693</v>
       </c>
       <c r="F16" t="n">
-        <v>1.282241951543313</v>
+        <v>1.28324195154331</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3075424543425541</v>
+        <v>0.3093436191388782</v>
       </c>
       <c r="H16" t="n">
         <v>10000</v>
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3898469247637776</v>
+        <v>0.384310931055895</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3489742646729042</v>
+        <v>0.3419904196608883</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01924195154331443</v>
+        <v>0.01575627943405548</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9964889135903584</v>
+        <v>1.000758048456689</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2681457838809136</v>
+        <v>0.268785960408484</v>
       </c>
       <c r="H17" t="n">
         <v>10000</v>
@@ -962,19 +962,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01707399055223004</v>
+        <v>0.01723804353881496</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01692278429128914</v>
+        <v>0.0171672060594157</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002077460143287749</v>
+        <v>0.002193156685766127</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03299029946971573</v>
+        <v>0.0330160280768869</v>
       </c>
       <c r="G18" t="n">
-        <v>0.007912638996252278</v>
+        <v>0.007958980457747532</v>
       </c>
       <c r="H18" t="n">
         <v>10000</v>
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01003021838415519</v>
+        <v>0.009887784976742737</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008978621768634327</v>
+        <v>0.008798937163775489</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0004950686124655774</v>
+        <v>0.0004053871240387778</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02563827180824161</v>
+        <v>0.02574811070217838</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006899017538090744</v>
+        <v>0.006915488388488837</v>
       </c>
       <c r="H19" t="n">
         <v>10000</v>
@@ -1022,19 +1022,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.707399055223004</v>
+        <v>1.723804353881496</v>
       </c>
       <c r="D20" t="n">
-        <v>1.692278429128914</v>
+        <v>1.71672060594157</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2077460143287749</v>
+        <v>0.2193156685766127</v>
       </c>
       <c r="F20" t="n">
-        <v>3.299029946971573</v>
+        <v>3.30160280768869</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7912638996252278</v>
+        <v>0.7958980457747531</v>
       </c>
       <c r="H20" t="n">
         <v>10000</v>
@@ -1052,19 +1052,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.003021838415519</v>
+        <v>0.9887784976742738</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8978621768634327</v>
+        <v>0.879893716377549</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04950686124655774</v>
+        <v>0.04053871240387778</v>
       </c>
       <c r="F21" t="n">
-        <v>2.563827180824161</v>
+        <v>2.574811070217838</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6899017538090745</v>
+        <v>0.6915488388488836</v>
       </c>
       <c r="H21" t="n">
         <v>10000</v>
@@ -1082,19 +1082,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9829260094477701</v>
+        <v>0.982761956461185</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9830772157087109</v>
+        <v>0.9828327939405843</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9670097005302842</v>
+        <v>0.9669839719231131</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9979225398567122</v>
+        <v>0.9978068433142339</v>
       </c>
       <c r="G22" t="n">
-        <v>0.007912638996252278</v>
+        <v>0.00795898045774753</v>
       </c>
       <c r="H22" t="n">
         <v>10000</v>
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9899697816158448</v>
+        <v>0.9901122150232573</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9910213782313657</v>
+        <v>0.9912010628362246</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9743617281917584</v>
+        <v>0.9742518892978216</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9995049313875344</v>
+        <v>0.9995946128759612</v>
       </c>
       <c r="G23" t="n">
-        <v>0.006899017538090744</v>
+        <v>0.006915488388488837</v>
       </c>
       <c r="H23" t="n">
         <v>10000</v>
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1520853</v>
+        <v>0.1521932</v>
       </c>
       <c r="D25" t="n">
         <v>0.152</v>
       </c>
       <c r="E25" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="F25" t="n">
         <v>0.175</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01128910839290822</v>
+        <v>0.01132220353947495</v>
       </c>
       <c r="H25" t="n">
         <v>10000</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1721087</v>
+        <v>0.1717572</v>
       </c>
       <c r="D26" t="n">
         <v>0.172</v>
@@ -1214,7 +1214,7 @@
         <v>0.196</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01199496028410356</v>
+        <v>0.01196648519143293</v>
       </c>
       <c r="H26" t="n">
         <v>10000</v>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.009769255806237564</v>
+        <v>0.009792654280026548</v>
       </c>
       <c r="D27" t="n">
-        <v>0.008397478433974787</v>
+        <v>0.008602521566025229</v>
       </c>
       <c r="E27" t="n">
         <v>0.0003974784339747794</v>
@@ -1244,7 +1244,7 @@
         <v>0.02660252156602522</v>
       </c>
       <c r="G27" t="n">
-        <v>0.007239018988678569</v>
+        <v>0.007192404719776145</v>
       </c>
       <c r="H27" t="n">
         <v>10000</v>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01656485248838752</v>
+        <v>0.01627825719973457</v>
       </c>
       <c r="D28" t="n">
         <v>0.01539747843397477</v>
@@ -1274,7 +1274,7 @@
         <v>0.03939747843397479</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01048441263328818</v>
+        <v>0.01038633028177624</v>
       </c>
       <c r="H28" t="n">
         <v>10000</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.06238249364406782</v>
+        <v>0.06253190677966104</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05362288135593222</v>
+        <v>0.05493220338983059</v>
       </c>
       <c r="E29" t="n">
         <v>0.002538135593220307</v>
@@ -1304,7 +1304,7 @@
         <v>0.1698728813559322</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04622543057601103</v>
+        <v>0.04592777081653666</v>
       </c>
       <c r="H29" t="n">
         <v>10000</v>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1057764097457627</v>
+        <v>0.1039463288135593</v>
       </c>
       <c r="D30" t="n">
         <v>0.09832203389830496</v>
@@ -1334,7 +1334,7 @@
         <v>0.2515762711864407</v>
       </c>
       <c r="G30" t="n">
-        <v>0.06694919423036137</v>
+        <v>0.06632288023151184</v>
       </c>
       <c r="H30" t="n">
         <v>10000</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.238249364406783</v>
+        <v>6.253190677966105</v>
       </c>
       <c r="D31" t="n">
-        <v>5.362288135593221</v>
+        <v>5.493220338983059</v>
       </c>
       <c r="E31" t="n">
         <v>0.2538135593220308</v>
@@ -1364,7 +1364,7 @@
         <v>16.98728813559322</v>
       </c>
       <c r="G31" t="n">
-        <v>4.622543057601103</v>
+        <v>4.592777081653666</v>
       </c>
       <c r="H31" t="n">
         <v>10000</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10.57764097457627</v>
+        <v>10.39463288135593</v>
       </c>
       <c r="D32" t="n">
         <v>9.832203389830497</v>
@@ -1394,7 +1394,7 @@
         <v>25.15762711864406</v>
       </c>
       <c r="G32" t="n">
-        <v>6.694919423036136</v>
+        <v>6.632288023151185</v>
       </c>
       <c r="H32" t="n">
         <v>10000</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9376175063559322</v>
+        <v>0.937468093220339</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9463771186440678</v>
+        <v>0.9450677966101694</v>
       </c>
       <c r="E33" t="n">
         <v>0.8301271186440677</v>
@@ -1424,7 +1424,7 @@
         <v>0.9974618644067796</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04622543057601103</v>
+        <v>0.04592777081653666</v>
       </c>
       <c r="H33" t="n">
         <v>10000</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.8942235902542374</v>
+        <v>0.8960536711864409</v>
       </c>
       <c r="D34" t="n">
         <v>0.901677966101695</v>
@@ -1454,7 +1454,7 @@
         <v>0.9961525423728813</v>
       </c>
       <c r="G34" t="n">
-        <v>0.06694919423036137</v>
+        <v>0.06632288023151184</v>
       </c>
       <c r="H34" t="n">
         <v>10000</v>
@@ -1502,19 +1502,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2898085.6253058</v>
+        <v>2897995.9243575</v>
       </c>
       <c r="D36" t="n">
-        <v>2897332.681</v>
+        <v>2896029.9795</v>
       </c>
       <c r="E36" t="n">
-        <v>2720240.4348</v>
+        <v>2722354.34795</v>
       </c>
       <c r="F36" t="n">
-        <v>3081412.644475</v>
+        <v>3081745.6311</v>
       </c>
       <c r="G36" t="n">
-        <v>91796.94693387992</v>
+        <v>91978.93302895459</v>
       </c>
       <c r="H36" t="n">
         <v>10000</v>
@@ -1532,19 +1532,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2173105.9151329</v>
+        <v>2172957.9761095</v>
       </c>
       <c r="D37" t="n">
-        <v>2172491.1705</v>
+        <v>2172639.756</v>
       </c>
       <c r="E37" t="n">
-        <v>2027142.9985</v>
+        <v>2027612.440225</v>
       </c>
       <c r="F37" t="n">
-        <v>2330312.874225</v>
+        <v>2321278.701975</v>
       </c>
       <c r="G37" t="n">
-        <v>76658.13864852587</v>
+        <v>75956.68918405191</v>
       </c>
       <c r="H37" t="n">
         <v>10000</v>
@@ -1562,19 +1562,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>248909.2572474509</v>
+        <v>248767.5488214137</v>
       </c>
       <c r="D38" t="n">
-        <v>247994.3163682816</v>
+        <v>246691.6148682814</v>
       </c>
       <c r="E38" t="n">
-        <v>70980.34284328175</v>
+        <v>73155.95749328162</v>
       </c>
       <c r="F38" t="n">
-        <v>432074.2798432813</v>
+        <v>432407.2664682814</v>
       </c>
       <c r="G38" t="n">
-        <v>91356.73348523377</v>
+        <v>91681.00845665956</v>
       </c>
       <c r="H38" t="n">
         <v>10000</v>
@@ -1592,19 +1592,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>476232.4494988185</v>
+        <v>476380.3885222184</v>
       </c>
       <c r="D39" t="n">
-        <v>476847.1941317185</v>
+        <v>476698.6086317184</v>
       </c>
       <c r="E39" t="n">
-        <v>319025.4904067186</v>
+        <v>328059.6626567187</v>
       </c>
       <c r="F39" t="n">
-        <v>622195.3661317185</v>
+        <v>621725.9244067183</v>
       </c>
       <c r="G39" t="n">
-        <v>76658.13864852587</v>
+        <v>75956.68918405191</v>
       </c>
       <c r="H39" t="n">
         <v>10000</v>
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.09395147881839223</v>
+        <v>0.09389799058603623</v>
       </c>
       <c r="D40" t="n">
-        <v>0.09360613188521694</v>
+        <v>0.09311442364689182</v>
       </c>
       <c r="E40" t="n">
-        <v>0.02679172422475701</v>
+        <v>0.02761291591512167</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1630876167466603</v>
+        <v>0.1632133034575181</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03448284851222964</v>
+        <v>0.03460524698565788</v>
       </c>
       <c r="H40" t="n">
         <v>10000</v>
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1797552384612145</v>
+        <v>0.1798110784495583</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1799872755015211</v>
+        <v>0.1799311914988193</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1204170424833847</v>
+        <v>0.1238270154678117</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2348493399098945</v>
+        <v>0.2346721478489381</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02893482375520653</v>
+        <v>0.02867005973946652</v>
       </c>
       <c r="H41" t="n">
         <v>10000</v>
@@ -1682,19 +1682,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9.395147881839225</v>
+        <v>9.389799058603623</v>
       </c>
       <c r="D42" t="n">
-        <v>9.360613188521693</v>
+        <v>9.311442364689182</v>
       </c>
       <c r="E42" t="n">
-        <v>2.679172422475701</v>
+        <v>2.761291591512168</v>
       </c>
       <c r="F42" t="n">
-        <v>16.30876167466603</v>
+        <v>16.32133034575181</v>
       </c>
       <c r="G42" t="n">
-        <v>3.448284851222964</v>
+        <v>3.460524698565788</v>
       </c>
       <c r="H42" t="n">
         <v>10000</v>
@@ -1712,19 +1712,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17.97552384612144</v>
+        <v>17.98110784495583</v>
       </c>
       <c r="D43" t="n">
-        <v>17.99872755015211</v>
+        <v>17.99311914988193</v>
       </c>
       <c r="E43" t="n">
-        <v>12.04170424833847</v>
+        <v>12.38270154678117</v>
       </c>
       <c r="F43" t="n">
-        <v>23.48493399098945</v>
+        <v>23.46721478489381</v>
       </c>
       <c r="G43" t="n">
-        <v>2.893482375520653</v>
+        <v>2.867005973946652</v>
       </c>
       <c r="H43" t="n">
         <v>10000</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9060485211816076</v>
+        <v>0.9061020094139638</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9063938681147831</v>
+        <v>0.9068855763531082</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8369123832533397</v>
+        <v>0.8367866965424819</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9732082757752429</v>
+        <v>0.9723870840848784</v>
       </c>
       <c r="G44" t="n">
-        <v>0.03448284851222964</v>
+        <v>0.03460524698565788</v>
       </c>
       <c r="H44" t="n">
         <v>10000</v>
@@ -1772,19 +1772,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.8202447615387854</v>
+        <v>0.8201889215504418</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8200127244984788</v>
+        <v>0.8200688085011807</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7651506600901055</v>
+        <v>0.765327852151062</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8795829575166153</v>
+        <v>0.8761729845321883</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02893482375520653</v>
+        <v>0.02867005973946652</v>
       </c>
       <c r="H45" t="n">
         <v>10000</v>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.5543777</v>
+        <v>0.5540385</v>
       </c>
       <c r="D47" t="n">
         <v>0.554</v>
@@ -1844,7 +1844,7 @@
         <v>0.585</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0159356279177732</v>
+        <v>0.01575108337266807</v>
       </c>
       <c r="H47" t="n">
         <v>10000</v>
@@ -1862,19 +1862,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.5539386000000002</v>
+        <v>0.5542855000000001</v>
       </c>
       <c r="D48" t="n">
         <v>0.554</v>
       </c>
       <c r="E48" t="n">
-        <v>0.523</v>
+        <v>0.524</v>
       </c>
       <c r="F48" t="n">
         <v>0.585</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01572008085647821</v>
+        <v>0.01563790408444861</v>
       </c>
       <c r="H48" t="n">
         <v>10000</v>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.01281643988055737</v>
+        <v>0.01262254552090242</v>
       </c>
       <c r="D49" t="n">
         <v>0.01092833443928332</v>
@@ -1901,10 +1901,10 @@
         <v>7.166556071658281e-05</v>
       </c>
       <c r="F49" t="n">
-        <v>0.03592833443928334</v>
+        <v>0.03607166556071661</v>
       </c>
       <c r="G49" t="n">
-        <v>0.00961958858098404</v>
+        <v>0.00963774938153839</v>
       </c>
       <c r="H49" t="n">
         <v>10000</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.01262557518248172</v>
+        <v>0.0125865135368281</v>
       </c>
       <c r="D50" t="n">
         <v>0.01092833443928332</v>
@@ -1931,10 +1931,10 @@
         <v>7.166556071658281e-05</v>
       </c>
       <c r="F50" t="n">
-        <v>0.03592833443928334</v>
+        <v>0.03507166556071661</v>
       </c>
       <c r="G50" t="n">
-        <v>0.009604700675467337</v>
+        <v>0.009449792802275233</v>
       </c>
       <c r="H50" t="n">
         <v>10000</v>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.02304818007159899</v>
+        <v>0.02269949415274457</v>
       </c>
       <c r="D51" t="n">
         <v>0.01965274463007155</v>
@@ -1961,10 +1961,10 @@
         <v>0.0001288782816227808</v>
       </c>
       <c r="F51" t="n">
-        <v>0.06461097852028638</v>
+        <v>0.06486873508353215</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0172991885340608</v>
+        <v>0.01733184763481904</v>
       </c>
       <c r="H51" t="n">
         <v>10000</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.02270494248210018</v>
+        <v>0.0226346967780429</v>
       </c>
       <c r="D52" t="n">
         <v>0.01965274463007155</v>
@@ -1991,10 +1991,10 @@
         <v>0.0001288782816227808</v>
       </c>
       <c r="F52" t="n">
-        <v>0.06461097852028638</v>
+        <v>0.06307040572792355</v>
       </c>
       <c r="G52" t="n">
-        <v>0.01727241517652658</v>
+        <v>0.01699383980075033</v>
       </c>
       <c r="H52" t="n">
         <v>10000</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.304818007159899</v>
+        <v>2.269949415274457</v>
       </c>
       <c r="D53" t="n">
         <v>1.965274463007155</v>
@@ -2021,10 +2021,10 @@
         <v>0.01288782816227808</v>
       </c>
       <c r="F53" t="n">
-        <v>6.461097852028638</v>
+        <v>6.486873508353215</v>
       </c>
       <c r="G53" t="n">
-        <v>1.72991885340608</v>
+        <v>1.733184763481904</v>
       </c>
       <c r="H53" t="n">
         <v>10000</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.270494248210018</v>
+        <v>2.26346967780429</v>
       </c>
       <c r="D54" t="n">
         <v>1.965274463007155</v>
@@ -2051,10 +2051,10 @@
         <v>0.01288782816227808</v>
       </c>
       <c r="F54" t="n">
-        <v>6.461097852028638</v>
+        <v>6.307040572792355</v>
       </c>
       <c r="G54" t="n">
-        <v>1.727241517652659</v>
+        <v>1.699383980075033</v>
       </c>
       <c r="H54" t="n">
         <v>10000</v>
@@ -2072,19 +2072,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.9769518199284009</v>
+        <v>0.9773005058472553</v>
       </c>
       <c r="D55" t="n">
         <v>0.9803472553699284</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9353890214797136</v>
+        <v>0.9351312649164678</v>
       </c>
       <c r="F55" t="n">
         <v>0.9998711217183772</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0172991885340608</v>
+        <v>0.01733184763481904</v>
       </c>
       <c r="H55" t="n">
         <v>10000</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.9772950575178997</v>
+        <v>0.9773653032219568</v>
       </c>
       <c r="D56" t="n">
         <v>0.9803472553699284</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9353890214797136</v>
+        <v>0.9369295942720764</v>
       </c>
       <c r="F56" t="n">
         <v>0.9998711217183772</v>
       </c>
       <c r="G56" t="n">
-        <v>0.01727241517652658</v>
+        <v>0.01699383980075033</v>
       </c>
       <c r="H56" t="n">
         <v>10000</v>
@@ -2162,19 +2162,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.492966296666667</v>
+        <v>2.491360781666667</v>
       </c>
       <c r="D58" t="n">
-        <v>2.488183333333333</v>
+        <v>2.487391666666666</v>
       </c>
       <c r="E58" t="n">
-        <v>2.322933333333333</v>
+        <v>2.322883333333333</v>
       </c>
       <c r="F58" t="n">
-        <v>2.690385</v>
+        <v>2.68352375</v>
       </c>
       <c r="G58" t="n">
-        <v>0.09341498496835558</v>
+        <v>0.09184026051559874</v>
       </c>
       <c r="H58" t="n">
         <v>10000</v>
@@ -2192,19 +2192,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2.389554116666667</v>
+        <v>2.388868896666667</v>
       </c>
       <c r="D59" t="n">
-        <v>2.386566666666667</v>
+        <v>2.385833333333333</v>
       </c>
       <c r="E59" t="n">
-        <v>2.228899166666666</v>
+        <v>2.22993125</v>
       </c>
       <c r="F59" t="n">
-        <v>2.569304166666667</v>
+        <v>2.566135</v>
       </c>
       <c r="G59" t="n">
-        <v>0.08626688114075676</v>
+        <v>0.08564661984144509</v>
       </c>
       <c r="H59" t="n">
         <v>10000</v>
@@ -2222,19 +2222,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.08425381026703661</v>
+        <v>0.08272131794765837</v>
       </c>
       <c r="D60" t="n">
-        <v>0.06935833333333319</v>
+        <v>0.06844999999999968</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003230498255615258</v>
+        <v>0.003168795695843777</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2501933790291765</v>
+        <v>0.2437196290291765</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0663682306036671</v>
+        <v>0.06482486024471659</v>
       </c>
       <c r="H60" t="n">
         <v>10000</v>
@@ -2252,19 +2252,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.08157577629929023</v>
+        <v>0.08153935194767856</v>
       </c>
       <c r="D61" t="n">
-        <v>0.07159999999999989</v>
+        <v>0.07124166666666643</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003413831588948471</v>
+        <v>0.003535751744384675</v>
       </c>
       <c r="F61" t="n">
-        <v>0.21423578763749</v>
+        <v>0.2123828709708232</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05795225352253213</v>
+        <v>0.0576866179952745</v>
       </c>
       <c r="H61" t="n">
         <v>10000</v>
@@ -2282,19 +2282,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.03452651274220164</v>
+        <v>0.03389851009846791</v>
       </c>
       <c r="D62" t="n">
-        <v>0.02842246982090611</v>
+        <v>0.02805024235358911</v>
       </c>
       <c r="E62" t="n">
-        <v>0.001323831395074584</v>
+        <v>0.00129854619777105</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1025271719069659</v>
+        <v>0.09987428284288187</v>
       </c>
       <c r="G62" t="n">
-        <v>0.02719715051879855</v>
+        <v>0.02656469014465819</v>
       </c>
       <c r="H62" t="n">
         <v>10000</v>
@@ -2312,19 +2312,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.03342907663078557</v>
+        <v>0.03341415023355723</v>
       </c>
       <c r="D63" t="n">
-        <v>0.02934108623107358</v>
+        <v>0.02919424420268244</v>
       </c>
       <c r="E63" t="n">
-        <v>0.001398959874716483</v>
+        <v>0.001448921743347203</v>
       </c>
       <c r="F63" t="n">
-        <v>0.08779204914599958</v>
+        <v>0.08703273926198195</v>
       </c>
       <c r="G63" t="n">
-        <v>0.02374835290348681</v>
+        <v>0.02363949766729543</v>
       </c>
       <c r="H63" t="n">
         <v>10000</v>
@@ -2342,19 +2342,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3.452651274220164</v>
+        <v>3.389851009846791</v>
       </c>
       <c r="D64" t="n">
-        <v>2.842246982090611</v>
+        <v>2.805024235358911</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1323831395074584</v>
+        <v>0.1298546197771051</v>
       </c>
       <c r="F64" t="n">
-        <v>10.25271719069659</v>
+        <v>9.987428284288187</v>
       </c>
       <c r="G64" t="n">
-        <v>2.719715051879855</v>
+        <v>2.656469014465818</v>
       </c>
       <c r="H64" t="n">
         <v>10000</v>
@@ -2372,19 +2372,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3.342907663078557</v>
+        <v>3.341415023355723</v>
       </c>
       <c r="D65" t="n">
-        <v>2.934108623107358</v>
+        <v>2.919424420268244</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1398959874716483</v>
+        <v>0.1448921743347203</v>
       </c>
       <c r="F65" t="n">
-        <v>8.779204914599958</v>
+        <v>8.703273926198195</v>
       </c>
       <c r="G65" t="n">
-        <v>2.374835290348681</v>
+        <v>2.363949766729542</v>
       </c>
       <c r="H65" t="n">
         <v>10000</v>
@@ -2402,19 +2402,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.9654734872577985</v>
+        <v>0.9661014899015321</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9715775301790939</v>
+        <v>0.9719497576464109</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8974728280930341</v>
+        <v>0.9001257171571181</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9986761686049254</v>
+        <v>0.998701453802229</v>
       </c>
       <c r="G66" t="n">
-        <v>0.02719715051879855</v>
+        <v>0.02656469014465819</v>
       </c>
       <c r="H66" t="n">
         <v>10000</v>
@@ -2432,19 +2432,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.9665709233692145</v>
+        <v>0.9665858497664427</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9706589137689264</v>
+        <v>0.9708057557973175</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9122079508540004</v>
+        <v>0.912967260738018</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9986010401252835</v>
+        <v>0.9985510782566528</v>
       </c>
       <c r="G67" t="n">
-        <v>0.02374835290348681</v>
+        <v>0.02363949766729542</v>
       </c>
       <c r="H67" t="n">
         <v>10000</v>
@@ -2492,19 +2492,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.4942098</v>
+        <v>0.493724</v>
       </c>
       <c r="D69" t="n">
         <v>0.494</v>
       </c>
       <c r="E69" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="F69" t="n">
         <v>0.525</v>
       </c>
       <c r="G69" t="n">
-        <v>0.01568437387715532</v>
+        <v>0.01580503096803009</v>
       </c>
       <c r="H69" t="n">
         <v>10000</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.7049666999999999</v>
+        <v>0.7049733</v>
       </c>
       <c r="D70" t="n">
         <v>0.705</v>
@@ -2531,10 +2531,10 @@
         <v>0.677</v>
       </c>
       <c r="F70" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="G70" t="n">
-        <v>0.01434236945090128</v>
+        <v>0.01450167635039815</v>
       </c>
       <c r="H70" t="n">
         <v>10000</v>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.1136203260783012</v>
+        <v>0.1141061260783012</v>
       </c>
       <c r="D71" t="n">
         <v>0.1138301260783012</v>
@@ -2561,10 +2561,10 @@
         <v>0.0828301260783012</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1438301260783012</v>
+        <v>0.1448301260783012</v>
       </c>
       <c r="G71" t="n">
-        <v>0.01568437387715532</v>
+        <v>0.01580503096803009</v>
       </c>
       <c r="H71" t="n">
         <v>10000</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.09713657392169875</v>
+        <v>0.09714317392169874</v>
       </c>
       <c r="D72" t="n">
         <v>0.09716987392169874</v>
@@ -2591,10 +2591,10 @@
         <v>0.06916987392169882</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1251698739216988</v>
+        <v>0.1261698739216988</v>
       </c>
       <c r="G72" t="n">
-        <v>0.01434236945090128</v>
+        <v>0.01450167635039815</v>
       </c>
       <c r="H72" t="n">
         <v>10000</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.1869277635371178</v>
+        <v>0.1877269999999999</v>
       </c>
       <c r="D73" t="n">
         <v>0.1872729257641921</v>
@@ -2621,10 +2621,10 @@
         <v>0.1362718340611353</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2366288209606986</v>
+        <v>0.2382740174672488</v>
       </c>
       <c r="G73" t="n">
-        <v>0.02580387711012343</v>
+        <v>0.02600238173452113</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.1598087520742358</v>
+        <v>0.1598196103711791</v>
       </c>
       <c r="D74" t="n">
         <v>0.1598635371179039</v>
@@ -2651,10 +2651,10 @@
         <v>0.113798034934498</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2059290393013101</v>
+        <v>0.2075742358078603</v>
       </c>
       <c r="G74" t="n">
-        <v>0.02359601611627537</v>
+        <v>0.02385810727079695</v>
       </c>
       <c r="H74" t="n">
         <v>10000</v>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>18.69277635371179</v>
+        <v>18.7727</v>
       </c>
       <c r="D75" t="n">
         <v>18.72729257641921</v>
@@ -2681,10 +2681,10 @@
         <v>13.62718340611353</v>
       </c>
       <c r="F75" t="n">
-        <v>23.66288209606986</v>
+        <v>23.82740174672488</v>
       </c>
       <c r="G75" t="n">
-        <v>2.580387711012343</v>
+        <v>2.600238173452113</v>
       </c>
       <c r="H75" t="n">
         <v>10000</v>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15.98087520742358</v>
+        <v>15.98196103711791</v>
       </c>
       <c r="D76" t="n">
         <v>15.98635371179039</v>
@@ -2711,10 +2711,10 @@
         <v>11.3798034934498</v>
       </c>
       <c r="F76" t="n">
-        <v>20.59290393013101</v>
+        <v>20.75742358078603</v>
       </c>
       <c r="G76" t="n">
-        <v>2.359601611627537</v>
+        <v>2.385810727079695</v>
       </c>
       <c r="H76" t="n">
         <v>10000</v>
@@ -2732,19 +2732,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.8130722364628821</v>
+        <v>0.812273</v>
       </c>
       <c r="D77" t="n">
         <v>0.8127270742358079</v>
       </c>
       <c r="E77" t="n">
-        <v>0.7633711790393014</v>
+        <v>0.7617259825327511</v>
       </c>
       <c r="F77" t="n">
         <v>0.8637281659388647</v>
       </c>
       <c r="G77" t="n">
-        <v>0.02580387711012343</v>
+        <v>0.02600238173452113</v>
       </c>
       <c r="H77" t="n">
         <v>10000</v>
@@ -2762,19 +2762,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.8401912479257641</v>
+        <v>0.8401803896288209</v>
       </c>
       <c r="D78" t="n">
         <v>0.8401364628820961</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7940709606986899</v>
+        <v>0.7924257641921397</v>
       </c>
       <c r="F78" t="n">
         <v>0.8862019650655021</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02359601611627537</v>
+        <v>0.02385810727079695</v>
       </c>
       <c r="H78" t="n">
         <v>10000</v>
@@ -2822,19 +2822,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.5880529999999999</v>
+        <v>0.5878383</v>
       </c>
       <c r="D80" t="n">
         <v>0.588</v>
       </c>
       <c r="E80" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="F80" t="n">
-        <v>0.619</v>
+        <v>0.618</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01555842528856137</v>
+        <v>0.01559235919534076</v>
       </c>
       <c r="H80" t="n">
         <v>10000</v>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.5838205999999999</v>
+        <v>0.583871</v>
       </c>
       <c r="D81" t="n">
         <v>0.584</v>
@@ -2861,10 +2861,10 @@
         <v>0.554</v>
       </c>
       <c r="F81" t="n">
-        <v>0.614</v>
+        <v>0.615</v>
       </c>
       <c r="G81" t="n">
-        <v>0.01549041028898499</v>
+        <v>0.01557587942306887</v>
       </c>
       <c r="H81" t="n">
         <v>10000</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.01237900544127406</v>
+        <v>0.01248640192435303</v>
       </c>
       <c r="D82" t="n">
-        <v>0.01041804910418043</v>
+        <v>0.01058195089581959</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0005819508958195829</v>
+        <v>0.0005778533510286401</v>
       </c>
       <c r="F82" t="n">
         <v>0.0355819508958195</v>
       </c>
       <c r="G82" t="n">
-        <v>0.009547115840337411</v>
+        <v>0.009499287456763482</v>
       </c>
       <c r="H82" t="n">
         <v>10000</v>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.01317295434638356</v>
+        <v>0.01322619044459193</v>
       </c>
       <c r="D83" t="n">
-        <v>0.01058195089581959</v>
+        <v>0.01141804910418043</v>
       </c>
       <c r="E83" t="n">
         <v>0.0005819508958195829</v>
@@ -2924,7 +2924,7 @@
         <v>0.0365819508958195</v>
       </c>
       <c r="G83" t="n">
-        <v>0.009980241184173089</v>
+        <v>0.01001382210353068</v>
       </c>
       <c r="H83" t="n">
         <v>10000</v>
@@ -2942,19 +2942,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.02099624220596513</v>
+        <v>0.02117839921215534</v>
       </c>
       <c r="D84" t="n">
-        <v>0.01767023072594249</v>
+        <v>0.01794822734946553</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0009870568373664731</v>
+        <v>0.0009801069217784588</v>
       </c>
       <c r="F84" t="n">
         <v>0.06035115362971299</v>
       </c>
       <c r="G84" t="n">
-        <v>0.01619302596667246</v>
+        <v>0.01611190342976091</v>
       </c>
       <c r="H84" t="n">
         <v>10000</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.02234287248171079</v>
+        <v>0.02243316713562187</v>
       </c>
       <c r="D85" t="n">
-        <v>0.01794822734946553</v>
+        <v>0.0193663477771524</v>
       </c>
       <c r="E85" t="n">
         <v>0.0009870568373664731</v>
@@ -2984,7 +2984,7 @@
         <v>0.06204727068092289</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0169276572476633</v>
+        <v>0.01698461441758102</v>
       </c>
       <c r="H85" t="n">
         <v>10000</v>
@@ -3002,19 +3002,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2.099624220596513</v>
+        <v>2.117839921215534</v>
       </c>
       <c r="D86" t="n">
-        <v>1.767023072594249</v>
+        <v>1.794822734946553</v>
       </c>
       <c r="E86" t="n">
-        <v>0.09870568373664731</v>
+        <v>0.09801069217784587</v>
       </c>
       <c r="F86" t="n">
         <v>6.035115362971299</v>
       </c>
       <c r="G86" t="n">
-        <v>1.619302596667246</v>
+        <v>1.611190342976091</v>
       </c>
       <c r="H86" t="n">
         <v>10000</v>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2.234287248171079</v>
+        <v>2.243316713562187</v>
       </c>
       <c r="D87" t="n">
-        <v>1.794822734946553</v>
+        <v>1.93663477771524</v>
       </c>
       <c r="E87" t="n">
         <v>0.09870568373664731</v>
@@ -3044,7 +3044,7 @@
         <v>6.204727068092289</v>
       </c>
       <c r="G87" t="n">
-        <v>1.69276572476633</v>
+        <v>1.698461441758102</v>
       </c>
       <c r="H87" t="n">
         <v>10000</v>
@@ -3062,19 +3062,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.9790037577940349</v>
+        <v>0.9788216007878447</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9823297692740575</v>
+        <v>0.9820517726505344</v>
       </c>
       <c r="E88" t="n">
         <v>0.939648846370287</v>
       </c>
       <c r="F88" t="n">
-        <v>0.9990129431626336</v>
+        <v>0.9990198930782216</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01619302596667246</v>
+        <v>0.01611190342976091</v>
       </c>
       <c r="H88" t="n">
         <v>10000</v>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.9776571275182893</v>
+        <v>0.9775668328643782</v>
       </c>
       <c r="D89" t="n">
-        <v>0.9820517726505344</v>
+        <v>0.9806336522228476</v>
       </c>
       <c r="E89" t="n">
         <v>0.9379527293190771</v>
@@ -3104,7 +3104,7 @@
         <v>0.9990129431626336</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0169276572476633</v>
+        <v>0.01698461441758102</v>
       </c>
       <c r="H89" t="n">
         <v>10000</v>
@@ -3152,19 +3152,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.4099403</v>
+        <v>0.4101543</v>
       </c>
       <c r="D91" t="n">
         <v>0.41</v>
       </c>
       <c r="E91" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="F91" t="n">
-        <v>0.4410249999999996</v>
+        <v>0.441</v>
       </c>
       <c r="G91" t="n">
-        <v>0.01553847741376334</v>
+        <v>0.01558544776797294</v>
       </c>
       <c r="H91" t="n">
         <v>10000</v>
@@ -3182,19 +3182,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.4151937</v>
+        <v>0.4151304</v>
       </c>
       <c r="D92" t="n">
         <v>0.415</v>
       </c>
       <c r="E92" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="F92" t="n">
         <v>0.445</v>
       </c>
       <c r="G92" t="n">
-        <v>0.01548386758292425</v>
+        <v>0.01558756212655798</v>
       </c>
       <c r="H92" t="n">
         <v>10000</v>
@@ -3212,19 +3212,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.01232939781021897</v>
+        <v>0.01244838467153283</v>
       </c>
       <c r="D93" t="n">
         <v>0.01024087591240874</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0002408759124087334</v>
+        <v>0.0007591240875912675</v>
       </c>
       <c r="F93" t="n">
         <v>0.03524087591240876</v>
       </c>
       <c r="G93" t="n">
-        <v>0.009529446107604261</v>
+        <v>0.009480248621080753</v>
       </c>
       <c r="H93" t="n">
         <v>10000</v>
@@ -3242,19 +3242,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.01337647810218977</v>
+        <v>0.01342605255474451</v>
       </c>
       <c r="D94" t="n">
         <v>0.01124087591240874</v>
       </c>
       <c r="E94" t="n">
-        <v>0.0007591240875912675</v>
+        <v>0.0002408759124087334</v>
       </c>
       <c r="F94" t="n">
         <v>0.03724087591240877</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0101098962439975</v>
+        <v>0.01016328660565769</v>
       </c>
       <c r="H94" t="n">
         <v>10000</v>
@@ -3272,19 +3272,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.03016299107142854</v>
+        <v>0.0304540839285714</v>
       </c>
       <c r="D95" t="n">
         <v>0.02505357142857139</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0005892857142856514</v>
+        <v>0.001857142857142922</v>
       </c>
       <c r="F95" t="n">
         <v>0.08621428571428573</v>
       </c>
       <c r="G95" t="n">
-        <v>0.02331310922753185</v>
+        <v>0.02319275109085827</v>
       </c>
       <c r="H95" t="n">
         <v>10000</v>
@@ -3302,19 +3302,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.03272459821428569</v>
+        <v>0.03284587857142854</v>
       </c>
       <c r="D96" t="n">
         <v>0.02749999999999996</v>
       </c>
       <c r="E96" t="n">
-        <v>0.001857142857142922</v>
+        <v>0.0005892857142856514</v>
       </c>
       <c r="F96" t="n">
         <v>0.09110714285714287</v>
       </c>
       <c r="G96" t="n">
-        <v>0.02473313902549389</v>
+        <v>0.02486375473169828</v>
       </c>
       <c r="H96" t="n">
         <v>10000</v>
@@ -3332,19 +3332,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3.016299107142854</v>
+        <v>3.045408392857139</v>
       </c>
       <c r="D97" t="n">
         <v>2.505357142857139</v>
       </c>
       <c r="E97" t="n">
-        <v>0.05892857142856514</v>
+        <v>0.1857142857142922</v>
       </c>
       <c r="F97" t="n">
         <v>8.621428571428574</v>
       </c>
       <c r="G97" t="n">
-        <v>2.331310922753185</v>
+        <v>2.319275109085827</v>
       </c>
       <c r="H97" t="n">
         <v>10000</v>
@@ -3362,19 +3362,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3.272459821428568</v>
+        <v>3.284587857142854</v>
       </c>
       <c r="D98" t="n">
         <v>2.749999999999996</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1857142857142922</v>
+        <v>0.05892857142856514</v>
       </c>
       <c r="F98" t="n">
         <v>9.110714285714288</v>
       </c>
       <c r="G98" t="n">
-        <v>2.47331390254939</v>
+        <v>2.486375473169828</v>
       </c>
       <c r="H98" t="n">
         <v>10000</v>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.9698370089285714</v>
+        <v>0.9695459160714287</v>
       </c>
       <c r="D99" t="n">
         <v>0.9749464285714287</v>
@@ -3401,10 +3401,10 @@
         <v>0.9137857142857143</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9994107142857144</v>
+        <v>0.9981428571428571</v>
       </c>
       <c r="G99" t="n">
-        <v>0.02331310922753185</v>
+        <v>0.02319275109085827</v>
       </c>
       <c r="H99" t="n">
         <v>10000</v>
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.9672754017857144</v>
+        <v>0.9671541214285715</v>
       </c>
       <c r="D100" t="n">
         <v>0.9725</v>
@@ -3431,10 +3431,10 @@
         <v>0.9088928571428572</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9981428571428571</v>
+        <v>0.9994107142857144</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0247331390254939</v>
+        <v>0.02486375473169828</v>
       </c>
       <c r="H100" t="n">
         <v>10000</v>
